--- a/tools/downloads/bar-rota-template.xlsx
+++ b/tools/downloads/bar-rota-template.xlsx
@@ -3074,6 +3074,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;8&amp;K808080Template from hospitalityapp.co.uk</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3258,6 +3261,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;8&amp;K808080Template from hospitalityapp.co.uk</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3388,11 +3394,14 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>Free to use and share. From HospitalityApp — the rota, till and compliance app for independent UK hospitality.</t>
+          <t>Free to use and share. From Hospitality App — the rota, till and compliance app for independent UK hospitality.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;8&amp;K808080Template from hospitalityapp.co.uk</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>